--- a/Employee_Reports_wi52/Emmanuel Richard Marasigan Velasco Q0615.xlsx
+++ b/Employee_Reports_wi52/Emmanuel Richard Marasigan Velasco Q0615.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1341,11 +1341,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1440,11 +1440,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1489,11 +1489,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1538,11 +1538,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1575,11 +1575,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1649,11 +1649,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1686,11 +1686,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1723,11 +1723,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1760,11 +1760,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1797,11 +1797,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1834,11 +1834,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7991</v>
+        <v>7983</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7925</v>
+        <v>7917</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7925</v>
+        <v>7917</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7910</v>
+        <v>7902</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7910</v>
+        <v>7902</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7915</v>
+        <v>7907</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
